--- a/nr-init/ig/all-profiles.xlsx
+++ b/nr-init/ig/all-profiles.xlsx
@@ -42,7 +42,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>LM_Access</t>
+    <t>AccessLogical</t>
   </si>
   <si>
     <t>Title</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T12:48:10+00:00</t>
+    <t>2026-03-16T13:14:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -350,7 +350,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-additional-information</t>
   </si>
   <si>
-    <t>LM_AdditionalInformation</t>
+    <t>AdditionalInformationLogical</t>
   </si>
   <si>
     <t>Informations complémentaires</t>
@@ -381,7 +381,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-administrative-file</t>
   </si>
   <si>
-    <t>LM_AdministrativeFile</t>
+    <t>AdministrativeFileLogical</t>
   </si>
   <si>
     <t>Dossier administratif</t>
@@ -422,7 +422,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-alert</t>
   </si>
   <si>
-    <t>LM_Alert</t>
+    <t>AlertLogical</t>
   </si>
   <si>
     <t>Alerte initiale</t>
@@ -476,7 +476,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-caller</t>
   </si>
   <si>
-    <t>LM_Caller</t>
+    <t>CallerLogical</t>
   </si>
   <si>
     <t>Personne à l'origine de l'appel au SAMU, avec ses coordonnées et ses caractéristiques de communication.</t>
@@ -578,7 +578,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-case-details</t>
   </si>
   <si>
-    <t>LM_CaseDetails</t>
+    <t>CaseDetailsLogical</t>
   </si>
   <si>
     <t>Détails du dossier</t>
@@ -641,7 +641,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-city</t>
   </si>
   <si>
-    <t>LM_City</t>
+    <t>CityLogical</t>
   </si>
   <si>
     <t>Commune</t>
@@ -677,7 +677,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-contact</t>
   </si>
   <si>
-    <t>LM_Contact</t>
+    <t>ContactLogical</t>
   </si>
   <si>
     <t>Coordonnées de contact avec canal, type et valeur (utilisé pour l'appelant).</t>
@@ -722,7 +722,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-coord</t>
   </si>
   <si>
-    <t>LM_Coord</t>
+    <t>CoordLogical</t>
   </si>
   <si>
     <t>Coordonnées géographiques</t>
@@ -780,7 +780,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-create-case-health</t>
   </si>
   <si>
-    <t>LM_CreateCaseHealth</t>
+    <t>CreateCaseHealthLogical</t>
   </si>
   <si>
     <t>Dossier de régulation médicale (RS-EDA)</t>
@@ -949,7 +949,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-custom-map</t>
   </si>
   <si>
-    <t>LM_CustomMap</t>
+    <t>CustomMapLogical</t>
   </si>
   <si>
     <t>Champ personnalisé</t>
@@ -997,7 +997,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-decision</t>
   </si>
   <si>
-    <t>LM_Decision</t>
+    <t>DecisionLogical</t>
   </si>
   <si>
     <t>Décision médicale</t>
@@ -1108,7 +1108,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-destination</t>
   </si>
   <si>
-    <t>LM_Destination</t>
+    <t>DestinationLogical</t>
   </si>
   <si>
     <t>Destination du patient à l'issue de la décision de régulation médicale.</t>
@@ -1139,7 +1139,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-detailed-address</t>
   </si>
   <si>
-    <t>LM_DetailedAddress</t>
+    <t>DetailedAddressLogical</t>
   </si>
   <si>
     <t>Adresse détaillée</t>
@@ -1198,7 +1198,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-detailed-name</t>
   </si>
   <si>
-    <t>LM_DetailedName</t>
+    <t>DetailedNameLogical</t>
   </si>
   <si>
     <t>Prénom &amp; nom usuel</t>
@@ -1240,7 +1240,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-external-id</t>
   </si>
   <si>
-    <t>LM_ExternalId</t>
+    <t>ExternalIdLogical</t>
   </si>
   <si>
     <t>Identifiant(s) patient(s)</t>
@@ -1276,7 +1276,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-external-info</t>
   </si>
   <si>
-    <t>LM_ExternalInfo</t>
+    <t>ExternalInfoLogical</t>
   </si>
   <si>
     <t>Information externe</t>
@@ -1319,7 +1319,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-external-location-id</t>
   </si>
   <si>
-    <t>LM_ExternalLocationId</t>
+    <t>ExternalLocationIdLogical</t>
   </si>
   <si>
     <t>Identifiant de localisation externe</t>
@@ -1349,7 +1349,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-general-practitioner</t>
   </si>
   <si>
-    <t>LM_GeneralPractitioner</t>
+    <t>GeneralPractitionerLogical</t>
   </si>
   <si>
     <t>lm-general-practitioner.detailedName</t>
@@ -1383,7 +1383,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-geometry</t>
   </si>
   <si>
-    <t>LM_Geometry</t>
+    <t>GeometryLogical</t>
   </si>
   <si>
     <t>Géométrie</t>
@@ -1420,7 +1420,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-health-motive</t>
   </si>
   <si>
-    <t>LM_HealthMotive</t>
+    <t>HealthMotiveLogical</t>
   </si>
   <si>
     <t>Motif de santé</t>
@@ -1450,7 +1450,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-highway</t>
   </si>
   <si>
-    <t>LM_Highway</t>
+    <t>HighwayLogical</t>
   </si>
   <si>
     <t>Informations relatives à une voie routière (autoroute, route nationale…).</t>
@@ -1489,7 +1489,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-hypothesis</t>
   </si>
   <si>
-    <t>LM_Hypothesis</t>
+    <t>HypothesisLogical</t>
   </si>
   <si>
     <t>Hypothèses de régulation médicale</t>
@@ -1530,7 +1530,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-identity</t>
   </si>
   <si>
-    <t>LM_Identity</t>
+    <t>IdentityLogical</t>
   </si>
   <si>
     <t>Identité</t>
@@ -1567,7 +1567,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-ins-strict-features</t>
   </si>
   <si>
-    <t>LM_InsStrictFeatures</t>
+    <t>InsStrictFeaturesLogical</t>
   </si>
   <si>
     <t>Traits stricts de l'identité</t>
@@ -1619,7 +1619,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-location-kind</t>
   </si>
   <si>
-    <t>LM_LocationKind</t>
+    <t>LocationKindLogical</t>
   </si>
   <si>
     <t>Type de lieu</t>
@@ -1643,7 +1643,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-location</t>
   </si>
   <si>
-    <t>LM_Location</t>
+    <t>LocationLogical</t>
   </si>
   <si>
     <t>Localisation de l'intervention, incluant l'adresse, la commune, l'accès, les coordonnées géographiques et les références externes.</t>
@@ -1729,7 +1729,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-main-diagnosis</t>
   </si>
   <si>
-    <t>LM_MainDiagnosis</t>
+    <t>MainDiagnosisLogical</t>
   </si>
   <si>
     <t>Hypothèse de régulation médicale principale</t>
@@ -1759,7 +1759,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-medical-note</t>
   </si>
   <si>
-    <t>LM_MedicalNote</t>
+    <t>MedicalNoteLogical</t>
   </si>
   <si>
     <t>Observation médicale</t>
@@ -1822,7 +1822,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-notes</t>
   </si>
   <si>
-    <t>LM_Notes</t>
+    <t>NotesLogical</t>
   </si>
   <si>
     <t>Note</t>
@@ -1849,7 +1849,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-operator</t>
   </si>
   <si>
-    <t>LM_Operator</t>
+    <t>OperatorLogical</t>
   </si>
   <si>
     <t>Opérateur ayant effectué une observation médicale dans le contexte de la régulation médicale (RS-EDA).</t>
@@ -1879,7 +1879,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-other-diagnosis</t>
   </si>
   <si>
-    <t>LM_OtherDiagnosis</t>
+    <t>OtherDiagnosisLogical</t>
   </si>
   <si>
     <t>Hypothèses de régulation médicale secondaires</t>
@@ -1900,7 +1900,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-patient-detail</t>
   </si>
   <si>
-    <t>LM_PatientDetail</t>
+    <t>PatientDetailLogical</t>
   </si>
   <si>
     <t>Informations patient</t>
@@ -1969,7 +1969,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-patient</t>
   </si>
   <si>
-    <t>LM_Patient</t>
+    <t>PatientLogical</t>
   </si>
   <si>
     <t>Patient</t>
@@ -2027,7 +2027,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-personal-contact</t>
   </si>
   <si>
-    <t>LM_PersonalContact</t>
+    <t>PersonalContactLogical</t>
   </si>
   <si>
     <t>Contact personnel</t>
@@ -2051,7 +2051,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-point</t>
   </si>
   <si>
-    <t>LM_Point</t>
+    <t>PointLogical</t>
   </si>
   <si>
     <t>Point géographique</t>
@@ -2085,7 +2085,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-qualification</t>
   </si>
   <si>
-    <t>LM_Qualification</t>
+    <t>QualificationLogical</t>
   </si>
   <si>
     <t>Qualification du dossier</t>
@@ -2168,7 +2168,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-risk-threat</t>
   </si>
   <si>
-    <t>LM_RiskThreat</t>
+    <t>RiskThreatLogical</t>
   </si>
   <si>
     <t>Risque et menace</t>
@@ -2192,7 +2192,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-way-name</t>
   </si>
   <si>
-    <t>LM_WayName</t>
+    <t>WayNameLogical</t>
   </si>
   <si>
     <t>Nom complet d'une voie (rue, avenue, boulevard…).</t>
@@ -2228,7 +2228,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/hubsante/StructureDefinition/lm-whats-happen</t>
   </si>
   <si>
-    <t>LM_WhatsHappen</t>
+    <t>WhatsHappenLogical</t>
   </si>
   <si>
     <t>Code et libellé décrivant la nature de l'événement déclenchant l'appel (nomenclature SAMU).</t>

--- a/nr-init/ig/all-profiles.xlsx
+++ b/nr-init/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T13:14:36+00:00</t>
+    <t>2026-03-16T13:47:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
